--- a/artfynd/A 70806-2021 artfynd.xlsx
+++ b/artfynd/A 70806-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 70806-2021 artfynd.xlsx
+++ b/artfynd/A 70806-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94205465</v>
+        <v>94205469</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565763.8300413935</v>
+        <v>565764</v>
       </c>
       <c r="R2" t="n">
-        <v>6964538.839110779</v>
+        <v>6964539</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +746,9 @@
           <t>2021-06-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>94205544</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565804.3984673603</v>
+        <v>565804</v>
       </c>
       <c r="R3" t="n">
-        <v>6964503.507368819</v>
+        <v>6964503</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,19 +847,9 @@
           <t>2021-06-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,43 +877,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94205375</v>
+        <v>89534240</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565745.3091474967</v>
+        <v>565685</v>
       </c>
       <c r="R4" t="n">
-        <v>6964525.657625921</v>
+        <v>6964489</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,27 +945,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,6 +959,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1028,19 +978,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94205488</v>
+        <v>89534975</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1071,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565786.3170850113</v>
+        <v>565980</v>
       </c>
       <c r="R5" t="n">
-        <v>6964514.125723156</v>
+        <v>6964291</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,22 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94205484</v>
+        <v>94205488</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1187,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565786.3170850113</v>
+        <v>565786</v>
       </c>
       <c r="R6" t="n">
-        <v>6964514.125723156</v>
+        <v>6964514</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1220,19 +1150,9 @@
           <t>2021-06-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,16 +1183,11 @@
         <v>94205514</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1303,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565800.2580488939</v>
+        <v>565800</v>
       </c>
       <c r="R7" t="n">
-        <v>6964527.215717063</v>
+        <v>6964527</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1336,19 +1251,9 @@
           <t>2021-06-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,53 +1281,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>94205574</v>
+        <v>96115082</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bodberget, Jmt</t>
+          <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565830.7879387304</v>
+        <v>565696</v>
       </c>
       <c r="R8" t="n">
-        <v>6964489.852909373</v>
+        <v>6964474</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1449,22 +1347,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,7 +1361,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1492,53 +1379,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>94205469</v>
+        <v>96117558</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bodberget, Jmt</t>
+          <t>Stormyran, Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565763.8300413935</v>
+        <v>565850</v>
       </c>
       <c r="R9" t="n">
-        <v>6964538.839110779</v>
+        <v>6964536</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1565,22 +1445,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,7 +1459,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1608,55 +1477,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>94205554</v>
+        <v>96117609</v>
       </c>
       <c r="B10" t="n">
-        <v>6202</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105336</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bodberget, Jmt</t>
+          <t>Stormyran, Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>565804.3984673603</v>
+        <v>565799</v>
       </c>
       <c r="R10" t="n">
-        <v>6964503.507368819</v>
+        <v>6964515</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1683,22 +1543,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,7 +1557,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1726,54 +1575,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>94205510</v>
+        <v>96119709</v>
       </c>
       <c r="B11" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bodberget, Jmt</t>
+          <t>Stormyran, Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>565800.2580488939</v>
+        <v>565703</v>
       </c>
       <c r="R11" t="n">
-        <v>6964527.215717063</v>
+        <v>6964572</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1800,27 +1641,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1847,37 +1673,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>94205575</v>
+        <v>94205587</v>
       </c>
       <c r="B12" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1890,10 +1711,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565830.7879387304</v>
+        <v>565843</v>
       </c>
       <c r="R12" t="n">
-        <v>6964489.852909373</v>
+        <v>6964516</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1923,19 +1744,9 @@
           <t>2021-06-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1963,37 +1774,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>94205587</v>
+        <v>89534338</v>
       </c>
       <c r="B13" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6457</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2006,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565843.0981189084</v>
+        <v>565684</v>
       </c>
       <c r="R13" t="n">
-        <v>6964515.721231614</v>
+        <v>6964497</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2036,22 +1842,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2079,15 +1875,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96119554</v>
+        <v>89534137</v>
       </c>
       <c r="B14" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,17 +1904,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stormyran, Bräcke, Jmt</t>
+          <t>Bodberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>565702.6901194605</v>
+        <v>565624</v>
       </c>
       <c r="R14" t="n">
-        <v>6964571.929210692</v>
+        <v>6964521</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2150,22 +1943,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2174,6 +1957,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2192,15 +1976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96119709</v>
+        <v>89534227</v>
       </c>
       <c r="B15" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,35 +1987,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stormyran, Bräcke, Jmt</t>
+          <t>Bodberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>565702.6901194605</v>
+        <v>565684</v>
       </c>
       <c r="R15" t="n">
-        <v>6964571.929210692</v>
+        <v>6964488</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2263,22 +2044,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,6 +2058,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2305,15 +2077,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96117558</v>
+        <v>89534331</v>
       </c>
       <c r="B16" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2321,35 +2088,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stormyran, Bräcke, Jmt</t>
+          <t>Bodberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>565850.0223691318</v>
+        <v>565684</v>
       </c>
       <c r="R16" t="n">
-        <v>6964535.991131883</v>
+        <v>6964497</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2376,22 +2145,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,6 +2159,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2418,15 +2178,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96117609</v>
+        <v>94205465</v>
       </c>
       <c r="B17" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2434,35 +2189,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stormyran, Bräcke, Jmt</t>
+          <t>Bodberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>565799.1223532794</v>
+        <v>565764</v>
       </c>
       <c r="R17" t="n">
-        <v>6964515.297326101</v>
+        <v>6964539</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2489,22 +2246,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,6 +2260,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2531,52 +2279,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96114774</v>
+        <v>94205484</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stormyran, Bräcke, Jmt</t>
+          <t>Bodberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>565927.776812512</v>
+        <v>565786</v>
       </c>
       <c r="R18" t="n">
-        <v>6964382.904834808</v>
+        <v>6964514</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2603,27 +2347,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>En blomstängel</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,6 +2361,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2650,15 +2380,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96117730</v>
+        <v>94205574</v>
       </c>
       <c r="B19" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,17 +2409,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bräcke, Jmt</t>
+          <t>Bodberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>565836.8701603832</v>
+        <v>565831</v>
       </c>
       <c r="R19" t="n">
-        <v>6964483.569428912</v>
+        <v>6964490</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2721,22 +2448,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,6 +2462,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2760,6 +2478,923 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>96115155</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bräcke, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>565689</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6964485</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2021-09-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2021-09-15</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>96117730</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bräcke, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>565836</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6964484</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-09-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-09-15</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>96119554</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stormyran, Bräcke, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>565703</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6964572</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2021-09-15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2021-09-15</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>94205575</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bodberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>565831</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6964490</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2021-06-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2021-06-09</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>94205375</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bodberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>565745</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6964525</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2021-06-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2021-06-09</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>94205510</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bodberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>565800</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6964527</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2021-06-09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2021-06-09</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>94205554</v>
+      </c>
+      <c r="B26" t="n">
+        <v>6274</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>105336</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vanlig flatbagge</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Peltis ferruginea</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bodberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>565804</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6964503</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2021-06-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2021-06-09</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>96114774</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stormyran, Bräcke, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>565928</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6964383</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2021-09-15</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2021-09-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>En blomstängel</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>96114917</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bräcke, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>565875</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6964431</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2021-09-15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2021-09-15</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 70806-2021 artfynd.xlsx
+++ b/artfynd/A 70806-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94205469</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94205544</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89534240</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89534975</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94205488</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94205514</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96115082</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1474,6 +1514,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96117558</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1572,6 +1617,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96117609</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1670,6 +1720,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96119709</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1771,6 +1826,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94205587</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1872,6 +1932,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89534338</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1973,6 +2038,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89534137</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2074,6 +2144,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89534227</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2175,6 +2250,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89534331</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2276,6 +2356,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94205465</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2377,6 +2462,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94205484</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2478,6 +2568,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94205574</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2576,6 +2671,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96115155</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2674,6 +2774,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96117730</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2772,6 +2877,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96119554</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2873,6 +2983,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94205575</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2979,6 +3094,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94205375</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3085,6 +3205,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94205510</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3188,6 +3313,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94205554</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3292,6 +3422,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96114774</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3395,8 +3530,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96114917</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>